--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/30.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/30.xlsx
@@ -426,13 +426,13 @@
         <v>-22.28924154393712</v>
       </c>
       <c r="E2">
-        <v>-16.92186766947826</v>
+        <v>-6.741769415949349</v>
       </c>
       <c r="F2">
-        <v>-0.03972284931395244</v>
+        <v>3.247812235237223</v>
       </c>
       <c r="G2">
-        <v>-16.70015982478364</v>
+        <v>-15.02702629777212</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-21.79016091532928</v>
       </c>
       <c r="E3">
-        <v>-15.90994603660643</v>
+        <v>-6.693658615962535</v>
       </c>
       <c r="F3">
-        <v>0.8696572287445392</v>
+        <v>3.166865829370461</v>
       </c>
       <c r="G3">
-        <v>-16.27281618027037</v>
+        <v>-14.143045149061</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-20.95655872390497</v>
       </c>
       <c r="E4">
-        <v>-18.06231458000822</v>
+        <v>-7.492038735356975</v>
       </c>
       <c r="F4">
-        <v>0.5007943363193501</v>
+        <v>2.929425910501622</v>
       </c>
       <c r="G4">
-        <v>-15.31371216132227</v>
+        <v>-13.92617190124951</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.81673849122699</v>
       </c>
       <c r="E5">
-        <v>-18.43322542379469</v>
+        <v>-7.815112891104063</v>
       </c>
       <c r="F5">
-        <v>0.2059758925607977</v>
+        <v>3.237822124359461</v>
       </c>
       <c r="G5">
-        <v>-16.19596369174177</v>
+        <v>-13.8549064061459</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.42143622432825</v>
       </c>
       <c r="E6">
-        <v>-19.70997242358288</v>
+        <v>-8.461551927390977</v>
       </c>
       <c r="F6">
-        <v>0.7000291222036733</v>
+        <v>3.791340536379702</v>
       </c>
       <c r="G6">
-        <v>-15.07205380973505</v>
+        <v>-12.84914577061</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-16.81803416741465</v>
       </c>
       <c r="E7">
-        <v>-16.95242284519502</v>
+        <v>-10.21079316675961</v>
       </c>
       <c r="F7">
-        <v>0.5548618767000739</v>
+        <v>3.470951219264132</v>
       </c>
       <c r="G7">
-        <v>-15.5234920160797</v>
+        <v>-12.17551100823259</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-15.08546052431491</v>
       </c>
       <c r="E8">
-        <v>-19.89849914525082</v>
+        <v>-10.337084016725</v>
       </c>
       <c r="F8">
-        <v>0.8896159129475905</v>
+        <v>3.662022444393866</v>
       </c>
       <c r="G8">
-        <v>-14.67424029729187</v>
+        <v>-11.29901094814731</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.27516069822636</v>
       </c>
       <c r="E9">
-        <v>-20.11562488010153</v>
+        <v>-10.57613455415948</v>
       </c>
       <c r="F9">
-        <v>0.8072082669822901</v>
+        <v>3.785717578449499</v>
       </c>
       <c r="G9">
-        <v>-14.57220326106509</v>
+        <v>-11.29684533550898</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.46587942299006</v>
       </c>
       <c r="E10">
-        <v>-20.68976481364583</v>
+        <v>-11.2949723702608</v>
       </c>
       <c r="F10">
-        <v>1.018039368138403</v>
+        <v>3.783492583605579</v>
       </c>
       <c r="G10">
-        <v>-13.11191851907785</v>
+        <v>-10.56759910259626</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.696013742420952</v>
       </c>
       <c r="E11">
-        <v>-21.3310787871579</v>
+        <v>-13.1069686327476</v>
       </c>
       <c r="F11">
-        <v>0.6143767611216072</v>
+        <v>4.079241283957476</v>
       </c>
       <c r="G11">
-        <v>-13.08873510710877</v>
+        <v>-9.649545126226526</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-8.032393720950376</v>
       </c>
       <c r="E12">
-        <v>-20.30353277328208</v>
+        <v>-13.06183983849201</v>
       </c>
       <c r="F12">
-        <v>1.431744273179338</v>
+        <v>4.129529812246628</v>
       </c>
       <c r="G12">
-        <v>-11.95729322695668</v>
+        <v>-8.80593522650009</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.498613254826224</v>
       </c>
       <c r="E13">
-        <v>-22.36144898473462</v>
+        <v>-13.46318126165549</v>
       </c>
       <c r="F13">
-        <v>1.522511802973691</v>
+        <v>4.192429405876</v>
       </c>
       <c r="G13">
-        <v>-11.53559009613252</v>
+        <v>-8.426836836658303</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.147351884880643</v>
       </c>
       <c r="E14">
-        <v>-23.37179239730301</v>
+        <v>-15.21330298182499</v>
       </c>
       <c r="F14">
-        <v>1.667363440496824</v>
+        <v>4.524381075199846</v>
       </c>
       <c r="G14">
-        <v>-11.99472608290406</v>
+        <v>-8.120567777930212</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.986529901890402</v>
       </c>
       <c r="E15">
-        <v>-22.92931756917842</v>
+        <v>-15.56245515148068</v>
       </c>
       <c r="F15">
-        <v>1.634954394229696</v>
+        <v>4.58071834226424</v>
       </c>
       <c r="G15">
-        <v>-11.47449475658358</v>
+        <v>-7.090874446727586</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.039843729740026</v>
       </c>
       <c r="E16">
-        <v>-23.14874002989177</v>
+        <v>-15.84027591663243</v>
       </c>
       <c r="F16">
-        <v>1.618623959250907</v>
+        <v>4.979209451585359</v>
       </c>
       <c r="G16">
-        <v>-10.64529094551091</v>
+        <v>-6.186113076443504</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.290823531961144</v>
       </c>
       <c r="E17">
-        <v>-25.32287140063566</v>
+        <v>-17.16108433536573</v>
       </c>
       <c r="F17">
-        <v>1.608686863886924</v>
+        <v>4.813774540837464</v>
       </c>
       <c r="G17">
-        <v>-9.703736351704265</v>
+        <v>-5.770231906057521</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.731541363067097</v>
       </c>
       <c r="E18">
-        <v>-25.66778729474002</v>
+        <v>-18.27938216990039</v>
       </c>
       <c r="F18">
-        <v>2.11965369916016</v>
+        <v>5.165472832309245</v>
       </c>
       <c r="G18">
-        <v>-9.801542676321141</v>
+        <v>-5.31671163090146</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.328111230066288</v>
       </c>
       <c r="E19">
-        <v>-26.26241086653837</v>
+        <v>-18.67549054679458</v>
       </c>
       <c r="F19">
-        <v>2.331773739995029</v>
+        <v>5.444738678080236</v>
       </c>
       <c r="G19">
-        <v>-8.113863385820233</v>
+        <v>-4.674789583072298</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.054660784332757</v>
       </c>
       <c r="E20">
-        <v>-26.16237246535723</v>
+        <v>-18.85756733127507</v>
       </c>
       <c r="F20">
-        <v>2.374666604111987</v>
+        <v>5.619711411103965</v>
       </c>
       <c r="G20">
-        <v>-8.276360045288012</v>
+        <v>-4.049594575838399</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.8754340416129975</v>
       </c>
       <c r="E21">
-        <v>-26.46510419203531</v>
+        <v>-20.33471508390889</v>
       </c>
       <c r="F21">
-        <v>2.810967715166487</v>
+        <v>5.795547302961411</v>
       </c>
       <c r="G21">
-        <v>-8.473024824591985</v>
+        <v>-3.558570954630995</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.7654455378442999</v>
       </c>
       <c r="E22">
-        <v>-27.5751786681468</v>
+        <v>-20.59025387030294</v>
       </c>
       <c r="F22">
-        <v>2.922552117793192</v>
+        <v>5.763494454677486</v>
       </c>
       <c r="G22">
-        <v>-7.95953574617805</v>
+        <v>-3.33774634488086</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.7031072863505986</v>
       </c>
       <c r="E23">
-        <v>-28.18793516058935</v>
+        <v>-20.27110865246914</v>
       </c>
       <c r="F23">
-        <v>3.20585873975504</v>
+        <v>6.018792318015877</v>
       </c>
       <c r="G23">
-        <v>-7.701081169263904</v>
+        <v>-3.564659211017471</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.6762301740733304</v>
       </c>
       <c r="E24">
-        <v>-29.67233234359066</v>
+        <v>-20.57613295179852</v>
       </c>
       <c r="F24">
-        <v>2.726222416390486</v>
+        <v>6.156496801587656</v>
       </c>
       <c r="G24">
-        <v>-7.804377889755892</v>
+        <v>-3.036959849794107</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.6805087532482139</v>
       </c>
       <c r="E25">
-        <v>-29.60851202176768</v>
+        <v>-20.92659338302153</v>
       </c>
       <c r="F25">
-        <v>3.546728612537425</v>
+        <v>5.958318184141902</v>
       </c>
       <c r="G25">
-        <v>-8.405145465223038</v>
+        <v>-3.472442490570168</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.7154922570601026</v>
       </c>
       <c r="E26">
-        <v>-28.79246206479176</v>
+        <v>-21.650892672015</v>
       </c>
       <c r="F26">
-        <v>2.933274505455028</v>
+        <v>5.78138553384315</v>
       </c>
       <c r="G26">
-        <v>-8.403931468988171</v>
+        <v>-3.558568343886404</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.7872551910816459</v>
       </c>
       <c r="E27">
-        <v>-27.26839756042702</v>
+        <v>-21.09301256080741</v>
       </c>
       <c r="F27">
-        <v>3.31498289119543</v>
+        <v>5.595889221334257</v>
       </c>
       <c r="G27">
-        <v>-8.668330711336282</v>
+        <v>-3.587670313843544</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.8977235184848482</v>
       </c>
       <c r="E28">
-        <v>-27.6363679305955</v>
+        <v>-21.35893437551353</v>
       </c>
       <c r="F28">
-        <v>2.831822692899367</v>
+        <v>6.071373767275979</v>
       </c>
       <c r="G28">
-        <v>-7.836234195256655</v>
+        <v>-3.136645910516586</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.049869232006832</v>
       </c>
       <c r="E29">
-        <v>-29.00158248481387</v>
+        <v>-21.63582482132852</v>
       </c>
       <c r="F29">
-        <v>3.280613927653278</v>
+        <v>5.760615049585355</v>
       </c>
       <c r="G29">
-        <v>-7.50525966046286</v>
+        <v>-4.113680523316457</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.236782227764795</v>
       </c>
       <c r="E30">
-        <v>-27.85633030878107</v>
+        <v>-21.01317537951023</v>
       </c>
       <c r="F30">
-        <v>3.311984201197295</v>
+        <v>5.936994350459037</v>
       </c>
       <c r="G30">
-        <v>-8.740840226237568</v>
+        <v>-3.648333575162652</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.450610775293755</v>
       </c>
       <c r="E31">
-        <v>-27.63184093025144</v>
+        <v>-21.1051565507212</v>
       </c>
       <c r="F31">
-        <v>3.343049635537082</v>
+        <v>6.004870775444429</v>
       </c>
       <c r="G31">
-        <v>-8.528661097200903</v>
+        <v>-3.634193782457182</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.675275504305053</v>
       </c>
       <c r="E32">
-        <v>-27.50585741792409</v>
+        <v>-20.47335758435431</v>
       </c>
       <c r="F32">
-        <v>2.542712528913506</v>
+        <v>5.947615677297732</v>
       </c>
       <c r="G32">
-        <v>-8.598732176654089</v>
+        <v>-3.623421850274249</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.898903557182249</v>
       </c>
       <c r="E33">
-        <v>-27.09637154735262</v>
+        <v>-21.17765500760741</v>
       </c>
       <c r="F33">
-        <v>2.677643638420712</v>
+        <v>6.101393801953432</v>
       </c>
       <c r="G33">
-        <v>-7.684461169196876</v>
+        <v>-4.400940750676652</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.107174592208111</v>
       </c>
       <c r="E34">
-        <v>-26.50347986467672</v>
+        <v>-20.03635668875586</v>
       </c>
       <c r="F34">
-        <v>3.759221418703554</v>
+        <v>6.276195891292184</v>
       </c>
       <c r="G34">
-        <v>-8.032875477859308</v>
+        <v>-4.360108705271641</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.293148636722882</v>
       </c>
       <c r="E35">
-        <v>-25.85731909354857</v>
+        <v>-19.92636719324042</v>
       </c>
       <c r="F35">
-        <v>3.141815999109804</v>
+        <v>6.369791467399695</v>
       </c>
       <c r="G35">
-        <v>-9.209934898251916</v>
+        <v>-4.330200015235847</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.449765960717306</v>
       </c>
       <c r="E36">
-        <v>-26.15365487478641</v>
+        <v>-19.75163743959356</v>
       </c>
       <c r="F36">
-        <v>3.298413886404634</v>
+        <v>5.833976923512085</v>
       </c>
       <c r="G36">
-        <v>-8.884188379501824</v>
+        <v>-4.298301937821624</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-2.577686846881083</v>
       </c>
       <c r="E37">
-        <v>-26.74742703826318</v>
+        <v>-19.6095436205372</v>
       </c>
       <c r="F37">
-        <v>3.636139276525992</v>
+        <v>6.428477984418429</v>
       </c>
       <c r="G37">
-        <v>-8.24571643064982</v>
+        <v>-4.055732436372107</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.676344273321281</v>
       </c>
       <c r="E38">
-        <v>-25.73223267486739</v>
+        <v>-19.24666924066428</v>
       </c>
       <c r="F38">
-        <v>2.907354889421432</v>
+        <v>6.772558609254065</v>
       </c>
       <c r="G38">
-        <v>-8.424737798007047</v>
+        <v>-4.473435906482686</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.750196279271834</v>
       </c>
       <c r="E39">
-        <v>-24.45105835180692</v>
+        <v>-18.35041454318893</v>
       </c>
       <c r="F39">
-        <v>3.51289146086787</v>
+        <v>6.510613925875611</v>
       </c>
       <c r="G39">
-        <v>-9.326949776197909</v>
+        <v>-4.616340233166453</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.800640781316143</v>
       </c>
       <c r="E40">
-        <v>-23.38928572340318</v>
+        <v>-17.90241594400232</v>
       </c>
       <c r="F40">
-        <v>2.767503277541597</v>
+        <v>6.840473139139985</v>
       </c>
       <c r="G40">
-        <v>-8.298281162247294</v>
+        <v>-4.342183332909056</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.833787118726654</v>
       </c>
       <c r="E41">
-        <v>-24.70398892148899</v>
+        <v>-17.45085804271034</v>
       </c>
       <c r="F41">
-        <v>3.378621388548098</v>
+        <v>6.806034592735998</v>
       </c>
       <c r="G41">
-        <v>-8.858001305880663</v>
+        <v>-4.942792958328441</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.85224834106327</v>
       </c>
       <c r="E42">
-        <v>-24.14716787916922</v>
+        <v>-16.68093572731363</v>
       </c>
       <c r="F42">
-        <v>3.407165272513764</v>
+        <v>6.728829094060279</v>
       </c>
       <c r="G42">
-        <v>-9.013285783415489</v>
+        <v>-4.679603796098311</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.862819252172113</v>
       </c>
       <c r="E43">
-        <v>-22.00982565434066</v>
+        <v>-15.97931712536504</v>
       </c>
       <c r="F43">
-        <v>3.352474799846135</v>
+        <v>6.684098911043911</v>
       </c>
       <c r="G43">
-        <v>-9.323912174866148</v>
+        <v>-5.003098547638567</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.868297027503093</v>
       </c>
       <c r="E44">
-        <v>-23.2005181154784</v>
+        <v>-15.60893789262816</v>
       </c>
       <c r="F44">
-        <v>3.312332115506471</v>
+        <v>6.382026453939043</v>
       </c>
       <c r="G44">
-        <v>-9.120206217399943</v>
+        <v>-5.406824091208326</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.876134000071603</v>
       </c>
       <c r="E45">
-        <v>-21.16948148772015</v>
+        <v>-15.32158550748592</v>
       </c>
       <c r="F45">
-        <v>2.729126672504702</v>
+        <v>6.492111511566681</v>
       </c>
       <c r="G45">
-        <v>-9.314884220070079</v>
+        <v>-4.79293882954313</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.889672556552922</v>
       </c>
       <c r="E46">
-        <v>-21.7394142181924</v>
+        <v>-14.92684769032892</v>
       </c>
       <c r="F46">
-        <v>3.54849966204461</v>
+        <v>7.061428546693114</v>
       </c>
       <c r="G46">
-        <v>-9.687235140516133</v>
+        <v>-5.404419595439911</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.915490303021293</v>
       </c>
       <c r="E47">
-        <v>-21.94429628605752</v>
+        <v>-15.16537076992515</v>
       </c>
       <c r="F47">
-        <v>3.238839359530099</v>
+        <v>6.97776509574517</v>
       </c>
       <c r="G47">
-        <v>-9.975552719435729</v>
+        <v>-5.477695363878687</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.954441710653605</v>
       </c>
       <c r="E48">
-        <v>-20.07425474209492</v>
+        <v>-13.95553615779127</v>
       </c>
       <c r="F48">
-        <v>3.101752838040809</v>
+        <v>6.521583167023482</v>
       </c>
       <c r="G48">
-        <v>-9.565827684795591</v>
+        <v>-5.202431507914658</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.009131684632063</v>
       </c>
       <c r="E49">
-        <v>-20.34945067768938</v>
+        <v>-13.78617650638741</v>
       </c>
       <c r="F49">
-        <v>2.270081906038939</v>
+        <v>6.717021545100775</v>
       </c>
       <c r="G49">
-        <v>-10.30721518542928</v>
+        <v>-5.360157031642175</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.079213128726708</v>
       </c>
       <c r="E50">
-        <v>-19.93569945908731</v>
+        <v>-13.27717969247305</v>
       </c>
       <c r="F50">
-        <v>2.862437495372031</v>
+        <v>6.4436785262598</v>
       </c>
       <c r="G50">
-        <v>-9.586062260749015</v>
+        <v>-5.512008380039688</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.167154306843492</v>
       </c>
       <c r="E51">
-        <v>-20.28876395381099</v>
+        <v>-11.88030105511419</v>
       </c>
       <c r="F51">
-        <v>2.791633619985146</v>
+        <v>6.362115815045355</v>
       </c>
       <c r="G51">
-        <v>-9.098984779991079</v>
+        <v>-5.295911828744059</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.275593348573311</v>
       </c>
       <c r="E52">
-        <v>-20.36216365755468</v>
+        <v>-11.95101363113072</v>
       </c>
       <c r="F52">
-        <v>3.169596128330088</v>
+        <v>6.539797309476238</v>
       </c>
       <c r="G52">
-        <v>-9.642920361826576</v>
+        <v>-5.264598558118247</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.406967652822204</v>
       </c>
       <c r="E53">
-        <v>-18.84427290182429</v>
+        <v>-11.47758076579086</v>
       </c>
       <c r="F53">
-        <v>2.592712785346484</v>
+        <v>6.354975288033223</v>
       </c>
       <c r="G53">
-        <v>-9.315760124880397</v>
+        <v>-5.800662745011538</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.565132132174203</v>
       </c>
       <c r="E54">
-        <v>-17.84851141421738</v>
+        <v>-10.8522940347813</v>
       </c>
       <c r="F54">
-        <v>2.697257721784199</v>
+        <v>6.440567178294885</v>
       </c>
       <c r="G54">
-        <v>-9.306861401941587</v>
+        <v>-6.042804084348113</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.749991154650365</v>
       </c>
       <c r="E55">
-        <v>-18.41639245829516</v>
+        <v>-10.60027717159071</v>
       </c>
       <c r="F55">
-        <v>2.665642251488953</v>
+        <v>6.372228524298731</v>
       </c>
       <c r="G55">
-        <v>-10.01978264892607</v>
+        <v>-6.605268120546741</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.964956025683877</v>
       </c>
       <c r="E56">
-        <v>-15.77038152324689</v>
+        <v>-11.00855030445533</v>
       </c>
       <c r="F56">
-        <v>3.267167867971037</v>
+        <v>5.989216288266324</v>
       </c>
       <c r="G56">
-        <v>-10.28209590634589</v>
+        <v>-6.248371502707782</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.205770954055097</v>
       </c>
       <c r="E57">
-        <v>-17.99310961970261</v>
+        <v>-10.39100100614392</v>
       </c>
       <c r="F57">
-        <v>2.74065423328206</v>
+        <v>6.229340117520233</v>
       </c>
       <c r="G57">
-        <v>-10.03888285635466</v>
+        <v>-6.388281305345543</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.475149348045542</v>
       </c>
       <c r="E58">
-        <v>-18.36733057291496</v>
+        <v>-9.077963245799378</v>
       </c>
       <c r="F58">
-        <v>1.987804116391368</v>
+        <v>5.909668166575488</v>
       </c>
       <c r="G58">
-        <v>-10.73565534267082</v>
+        <v>-6.527480985454521</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.765012217740004</v>
       </c>
       <c r="E59">
-        <v>-17.86264063914444</v>
+        <v>-9.791705071605138</v>
       </c>
       <c r="F59">
-        <v>2.277149536719624</v>
+        <v>5.483958561133182</v>
       </c>
       <c r="G59">
-        <v>-10.75323087525819</v>
+        <v>-7.11027750052874</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.077903617321625</v>
       </c>
       <c r="E60">
-        <v>-16.66839718232397</v>
+        <v>-9.600329246968363</v>
       </c>
       <c r="F60">
-        <v>2.808918334211961</v>
+        <v>5.969366948560442</v>
       </c>
       <c r="G60">
-        <v>-11.08353836480896</v>
+        <v>-6.516980570709063</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.402470842806903</v>
       </c>
       <c r="E61">
-        <v>-16.30139451039417</v>
+        <v>-9.097948498694453</v>
       </c>
       <c r="F61">
-        <v>3.045579587722169</v>
+        <v>6.054284547756225</v>
       </c>
       <c r="G61">
-        <v>-11.55411855049565</v>
+        <v>-6.958073701611426</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.741609986817602</v>
       </c>
       <c r="E62">
-        <v>-17.20414483038155</v>
+        <v>-8.812473365071039</v>
       </c>
       <c r="F62">
-        <v>2.884599636866529</v>
+        <v>5.82081085201199</v>
       </c>
       <c r="G62">
-        <v>-10.15786231960547</v>
+        <v>-7.358979641022783</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.083611036392285</v>
       </c>
       <c r="E63">
-        <v>-16.30931468439062</v>
+        <v>-8.624789745302037</v>
       </c>
       <c r="F63">
-        <v>1.88622307852087</v>
+        <v>5.687662389155609</v>
       </c>
       <c r="G63">
-        <v>-10.942863614006</v>
+        <v>-7.548859095134452</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.432676207994639</v>
       </c>
       <c r="E64">
-        <v>-16.2134461073796</v>
+        <v>-8.735830003282652</v>
       </c>
       <c r="F64">
-        <v>2.282084949705503</v>
+        <v>5.752048073905603</v>
       </c>
       <c r="G64">
-        <v>-10.4157333951035</v>
+        <v>-7.714442960081221</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.77770927989192</v>
       </c>
       <c r="E65">
-        <v>-17.22614439076917</v>
+        <v>-7.966435145724191</v>
       </c>
       <c r="F65">
-        <v>2.820725883171465</v>
+        <v>5.844869954858899</v>
       </c>
       <c r="G65">
-        <v>-10.90635757238846</v>
+        <v>-7.878264572428988</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.123213456132626</v>
       </c>
       <c r="E66">
-        <v>-17.02224663398804</v>
+        <v>-8.178631018732331</v>
       </c>
       <c r="F66">
-        <v>2.785846645309189</v>
+        <v>5.325687371684698</v>
       </c>
       <c r="G66">
-        <v>-11.3222517964974</v>
+        <v>-7.903732385915299</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.457250686377453</v>
       </c>
       <c r="E67">
-        <v>-15.27437180114527</v>
+        <v>-8.485466118199339</v>
       </c>
       <c r="F67">
-        <v>2.587744237664493</v>
+        <v>5.584394795253011</v>
       </c>
       <c r="G67">
-        <v>-10.10144151824692</v>
+        <v>-7.794167267660048</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.783535215985535</v>
       </c>
       <c r="E68">
-        <v>-15.19350877665086</v>
+        <v>-7.577893919863831</v>
       </c>
       <c r="F68">
-        <v>2.5719157933318</v>
+        <v>5.743370096993876</v>
       </c>
       <c r="G68">
-        <v>-10.60229720358445</v>
+        <v>-7.839899680662579</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.089780063407115</v>
       </c>
       <c r="E69">
-        <v>-17.81962167624187</v>
+        <v>-8.497448132871469</v>
       </c>
       <c r="F69">
-        <v>2.194428767876065</v>
+        <v>5.578173756057986</v>
       </c>
       <c r="G69">
-        <v>-11.35463547240557</v>
+        <v>-7.659078204909777</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.379953556772303</v>
       </c>
       <c r="E70">
-        <v>-16.46599458161977</v>
+        <v>-8.03380023341291</v>
       </c>
       <c r="F70">
-        <v>2.286370922647588</v>
+        <v>5.648664508566614</v>
       </c>
       <c r="G70">
-        <v>-12.02907303874475</v>
+        <v>-7.980641005452609</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.642503363307032</v>
       </c>
       <c r="E71">
-        <v>-15.17394715131092</v>
+        <v>-8.565166243522798</v>
       </c>
       <c r="F71">
-        <v>2.264266766871286</v>
+        <v>5.450184365386241</v>
       </c>
       <c r="G71">
-        <v>-11.76335275963354</v>
+        <v>-7.615553176459032</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.881841576232171</v>
       </c>
       <c r="E72">
-        <v>-16.00752158347195</v>
+        <v>-7.613437102381714</v>
       </c>
       <c r="F72">
-        <v>2.492813333303669</v>
+        <v>5.766342381808311</v>
       </c>
       <c r="G72">
-        <v>-10.79845810918234</v>
+        <v>-7.411471271771706</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.089222473063995</v>
       </c>
       <c r="E73">
-        <v>-14.68914279336368</v>
+        <v>-8.34580608097933</v>
       </c>
       <c r="F73">
-        <v>2.070430451351007</v>
+        <v>5.318969312047994</v>
       </c>
       <c r="G73">
-        <v>-11.48714773024441</v>
+        <v>-7.874520764685332</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.27193179813059</v>
       </c>
       <c r="E74">
-        <v>-17.50423926786836</v>
+        <v>-8.729151639472329</v>
       </c>
       <c r="F74">
-        <v>1.48902753581773</v>
+        <v>5.461201651843474</v>
       </c>
       <c r="G74">
-        <v>-11.12335483056802</v>
+        <v>-8.109725355643318</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.423596909320237</v>
       </c>
       <c r="E75">
-        <v>-16.86326585768493</v>
+        <v>-8.462731439407227</v>
       </c>
       <c r="F75">
-        <v>1.73886314450206</v>
+        <v>5.63084466899759</v>
       </c>
       <c r="G75">
-        <v>-10.8920402490508</v>
+        <v>-7.570825900124079</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.555589292223619</v>
       </c>
       <c r="E76">
-        <v>-17.62369808520441</v>
+        <v>-8.765591915636374</v>
       </c>
       <c r="F76">
-        <v>2.52546260611761</v>
+        <v>5.309847330208365</v>
       </c>
       <c r="G76">
-        <v>-11.53177188216801</v>
+        <v>-7.905229647938302</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-9.663554967780057</v>
       </c>
       <c r="E77">
-        <v>-17.73487539915874</v>
+        <v>-9.352154104253234</v>
       </c>
       <c r="F77">
-        <v>1.602003595681137</v>
+        <v>5.250262862924997</v>
       </c>
       <c r="G77">
-        <v>-11.24080309211614</v>
+        <v>-7.47587573008988</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-9.756886954572645</v>
       </c>
       <c r="E78">
-        <v>-17.67503593039061</v>
+        <v>-9.196358841036265</v>
       </c>
       <c r="F78">
-        <v>2.105846471290298</v>
+        <v>5.372675684241097</v>
       </c>
       <c r="G78">
-        <v>-10.59506805181166</v>
+        <v>-7.149020950260861</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-9.826530364891534</v>
       </c>
       <c r="E79">
-        <v>-17.0902222437415</v>
+        <v>-9.876796065228225</v>
       </c>
       <c r="F79">
-        <v>2.003708770525118</v>
+        <v>5.435152810495041</v>
       </c>
       <c r="G79">
-        <v>-9.958235650562875</v>
+        <v>-7.046220271241184</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-9.875194242602911</v>
       </c>
       <c r="E80">
-        <v>-19.03328554921724</v>
+        <v>-10.49090235135135</v>
       </c>
       <c r="F80">
-        <v>1.947126306709495</v>
+        <v>5.379064053651486</v>
       </c>
       <c r="G80">
-        <v>-10.87168818959077</v>
+        <v>-6.90130828196685</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-9.888931319846808</v>
       </c>
       <c r="E81">
-        <v>-18.66403598996071</v>
+        <v>-11.48725774817771</v>
       </c>
       <c r="F81">
-        <v>1.844672169596447</v>
+        <v>5.210367032071367</v>
       </c>
       <c r="G81">
-        <v>-10.42735643002313</v>
+        <v>-6.576377620901482</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-9.865719322918636</v>
       </c>
       <c r="E82">
-        <v>-21.01425106124336</v>
+        <v>-12.02984988849861</v>
       </c>
       <c r="F82">
-        <v>1.849036009074395</v>
+        <v>5.568024598638887</v>
       </c>
       <c r="G82">
-        <v>-9.538421393450381</v>
+        <v>-6.845482730375075</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-9.790064888702101</v>
       </c>
       <c r="E83">
-        <v>-20.60989855986938</v>
+        <v>-13.47828233803257</v>
       </c>
       <c r="F83">
-        <v>1.542755445563305</v>
+        <v>5.098045382456171</v>
       </c>
       <c r="G83">
-        <v>-10.5600684098232</v>
+        <v>-7.273010432382013</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.657031728014765</v>
       </c>
       <c r="E84">
-        <v>-22.01745510354437</v>
+        <v>-14.4640096670787</v>
       </c>
       <c r="F84">
-        <v>1.811121633048261</v>
+        <v>5.151698739135495</v>
       </c>
       <c r="G84">
-        <v>-9.671611139510615</v>
+        <v>-7.182268782628689</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.45343842515269</v>
       </c>
       <c r="E85">
-        <v>-21.75120103193226</v>
+        <v>-15.10504952864333</v>
       </c>
       <c r="F85">
-        <v>1.955930195466449</v>
+        <v>5.293485417268269</v>
       </c>
       <c r="G85">
-        <v>-10.02875708345803</v>
+        <v>-6.671009280095565</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.176422424240451</v>
       </c>
       <c r="E86">
-        <v>-22.94723867604506</v>
+        <v>-15.76493666320004</v>
       </c>
       <c r="F86">
-        <v>1.581097259169283</v>
+        <v>5.279343528967677</v>
       </c>
       <c r="G86">
-        <v>-9.600852128857673</v>
+        <v>-6.306611993046337</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.820883740031585</v>
       </c>
       <c r="E87">
-        <v>-24.4819831633316</v>
+        <v>-17.26476094966743</v>
       </c>
       <c r="F87">
-        <v>1.462940589568767</v>
+        <v>5.293664344627274</v>
       </c>
       <c r="G87">
-        <v>-8.966723153632984</v>
+        <v>-6.52102983556988</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.38973615848918</v>
       </c>
       <c r="E88">
-        <v>-25.24822988670584</v>
+        <v>-18.7119598954379</v>
       </c>
       <c r="F88">
-        <v>2.320716691902461</v>
+        <v>5.357157049317051</v>
       </c>
       <c r="G88">
-        <v>-9.303252047544373</v>
+        <v>-6.077479994007279</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.887184052564269</v>
       </c>
       <c r="E89">
-        <v>-26.9334244542343</v>
+        <v>-19.7924759665506</v>
       </c>
       <c r="F89">
-        <v>1.733684191499758</v>
+        <v>4.87783219209595</v>
       </c>
       <c r="G89">
-        <v>-8.848485141846055</v>
+        <v>-5.974796798494203</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.324790829011474</v>
       </c>
       <c r="E90">
-        <v>-27.71654567522132</v>
+        <v>-21.90113611396989</v>
       </c>
       <c r="F90">
-        <v>1.928340590748808</v>
+        <v>5.230206431368416</v>
       </c>
       <c r="G90">
-        <v>-9.255219568557072</v>
+        <v>-6.108446035602475</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.714504786667717</v>
       </c>
       <c r="E91">
-        <v>-29.91879221002864</v>
+        <v>-23.95181743129459</v>
       </c>
       <c r="F91">
-        <v>1.747276043844892</v>
+        <v>5.003473989548162</v>
       </c>
       <c r="G91">
-        <v>-8.913000556809351</v>
+        <v>-5.567604186107446</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.070646615903372</v>
       </c>
       <c r="E92">
-        <v>-31.26031892345584</v>
+        <v>-25.25884134164078</v>
       </c>
       <c r="F92">
-        <v>1.027153066304004</v>
+        <v>4.963263379081469</v>
       </c>
       <c r="G92">
-        <v>-8.592243170972877</v>
+        <v>-5.275386154768727</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-5.405006311885716</v>
       </c>
       <c r="E93">
-        <v>-32.38311260924963</v>
+        <v>-27.23763057093269</v>
       </c>
       <c r="F93">
-        <v>1.273057243294648</v>
+        <v>4.863370553977877</v>
       </c>
       <c r="G93">
-        <v>-8.862815518906675</v>
+        <v>-5.18817945319177</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.728141391728517</v>
       </c>
       <c r="E94">
-        <v>-33.14077464481545</v>
+        <v>-28.85812225923164</v>
       </c>
       <c r="F94">
-        <v>1.864723630948612</v>
+        <v>4.863279433563569</v>
       </c>
       <c r="G94">
-        <v>-8.595622779846073</v>
+        <v>-4.762662024519989</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.049213397625945</v>
       </c>
       <c r="E95">
-        <v>-38.78658989822316</v>
+        <v>-30.76124828460782</v>
       </c>
       <c r="F95">
-        <v>2.059789243694645</v>
+        <v>4.735836765377671</v>
       </c>
       <c r="G95">
-        <v>-8.689092657697111</v>
+        <v>-5.254017210290465</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.371430635992629</v>
       </c>
       <c r="E96">
-        <v>-38.60946374164187</v>
+        <v>-34.18943766167237</v>
       </c>
       <c r="F96">
-        <v>0.7446416770488434</v>
+        <v>4.608352678821632</v>
       </c>
       <c r="G96">
-        <v>-8.895316678321445</v>
+        <v>-5.811674865696854</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.703172751401849</v>
       </c>
       <c r="E97">
-        <v>-40.27269405107897</v>
+        <v>-36.29626624289742</v>
       </c>
       <c r="F97">
-        <v>0.8830950047527528</v>
+        <v>4.212644883973919</v>
       </c>
       <c r="G97">
-        <v>-9.213586024562588</v>
+        <v>-5.302710207659318</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.039059070039982</v>
       </c>
       <c r="E98">
-        <v>-41.85851265463259</v>
+        <v>-38.27531297129146</v>
       </c>
       <c r="F98">
-        <v>1.60325608719417</v>
+        <v>4.094360645793373</v>
       </c>
       <c r="G98">
-        <v>-8.292346939791694</v>
+        <v>-5.82559535585667</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-1.393656950871947</v>
       </c>
       <c r="E99">
-        <v>-45.40886874281697</v>
+        <v>-40.755315896475</v>
       </c>
       <c r="F99">
-        <v>0.4150873029886993</v>
+        <v>3.985919069092889</v>
       </c>
       <c r="G99">
-        <v>-9.386870280680846</v>
+        <v>-5.269705174538465</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.7524292423239326</v>
       </c>
       <c r="E100">
-        <v>-45.48974007373403</v>
+        <v>-43.02967879272665</v>
       </c>
       <c r="F100">
-        <v>1.076956171295115</v>
+        <v>3.535413113815184</v>
       </c>
       <c r="G100">
-        <v>-8.177625600968993</v>
+        <v>-5.616662687719056</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.1507736400721593</v>
       </c>
       <c r="E101">
-        <v>-47.69367385064206</v>
+        <v>-46.10325348894053</v>
       </c>
       <c r="F101">
-        <v>0.7373106255340678</v>
+        <v>3.310706858662178</v>
       </c>
       <c r="G101">
-        <v>-9.063972084279659</v>
+        <v>-5.354144486848842</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.4492597968303715</v>
       </c>
       <c r="E102">
-        <v>-49.34835996608115</v>
+        <v>-48.11727960141512</v>
       </c>
       <c r="F102">
-        <v>0.965966536463621</v>
+        <v>3.331616508643644</v>
       </c>
       <c r="G102">
-        <v>-8.21653222223806</v>
+        <v>-5.341800886422058</v>
       </c>
     </row>
   </sheetData>
